--- a/artfynd/A 50968-2023 artfynd.xlsx
+++ b/artfynd/A 50968-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430746</v>
       </c>
       <c r="B2" t="n">
-        <v>98001</v>
+        <v>98014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50968-2023 artfynd.xlsx
+++ b/artfynd/A 50968-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430746</v>
       </c>
       <c r="B2" t="n">
-        <v>98014</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50968-2023 artfynd.xlsx
+++ b/artfynd/A 50968-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430746</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>98018</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
+          <t>Robert Ennerfelt, Leif Andersson, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 50968-2023 artfynd.xlsx
+++ b/artfynd/A 50968-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Robert Ennerfelt, Leif Andersson, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 50968-2023 artfynd.xlsx
+++ b/artfynd/A 50968-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430746</v>
       </c>
       <c r="B2" t="n">
-        <v>98018</v>
+        <v>98024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50968-2023 artfynd.xlsx
+++ b/artfynd/A 50968-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430746</v>
       </c>
       <c r="B2" t="n">
-        <v>98024</v>
+        <v>98025</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50968-2023 artfynd.xlsx
+++ b/artfynd/A 50968-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430746</v>
       </c>
       <c r="B2" t="n">
-        <v>98025</v>
+        <v>98033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50968-2023 artfynd.xlsx
+++ b/artfynd/A 50968-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
+          <t>Robert Ennerfelt, Leif Andersson, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
